--- a/docs/Stage4/Final/04-Data_Classification.xlsx
+++ b/docs/Stage4/Final/04-Data_Classification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\databinex\sales&amp;marketing dashboard\Stage4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630E9FB0-1750-4B64-BC92-39F47C629844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DE6404-F933-4DDF-A85E-B7979047E825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="team1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="483">
   <si>
     <t>Entity</t>
   </si>
@@ -1497,9 +1497,6 @@
   </si>
   <si>
     <t>ردیف عنوان ثابت است و فیلتر دارد. راهنمای رنگ‌ها هم در ستون K است.</t>
-  </si>
-  <si>
-    <t>هیچ ردیفی حذف نشده است.</t>
   </si>
   <si>
     <t>موارد شناسایی‌شده</t>
@@ -1667,10 +1664,10 @@
     </r>
   </si>
   <si>
-    <t>مبنای Prodct و Product Category تیم 2 در نظر گرفته شد</t>
-  </si>
-  <si>
-    <t>مبنای Promotion تیم 1 در نظر گرفته شد</t>
+    <t>مبنای Product و Product Category تیم 2 در نظر گرفته شد و مقادیر تیم 1 حذف شد</t>
+  </si>
+  <si>
+    <t>مبنای Promotion تیم 1 در نظر گرفته شد و مقادیر تیم 2 حذف شد</t>
   </si>
 </sst>
 </file>
@@ -9513,13 +9510,11 @@
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="36" t="s">
-        <v>476</v>
-      </c>
+      <c r="A8" s="36"/>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="35" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9527,32 +9522,32 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="36" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="36" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="36" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
